--- a/tabular/genus/chaphama-refseqs-side-data.xlsx
+++ b/tabular/genus/chaphama-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF6BCE7-5621-B142-8931-73A60464F233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0231593A-83E6-0145-90CA-7CECF7698D12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7660" yWindow="6200" windowWidth="28040" windowHeight="17440" xr2:uid="{469403FE-80B6-3840-B15B-8B62EF5C2974}"/>
+    <workbookView xWindow="880" yWindow="560" windowWidth="27920" windowHeight="17440" xr2:uid="{469403FE-80B6-3840-B15B-8B62EF5C2974}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -269,36 +269,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF660066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -313,22 +289,205 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -339,6 +498,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A7BFF9F-E052-8C4B-BBA0-E4BFC77524D1}" name="Table1" displayName="Table1" ref="A1:O15" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:O15" xr:uid="{1D0B690B-FD1B-D144-8DF1-2968849E308F}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{6CFF3AA3-5109-0D4F-BF51-F203B8CA8552}" name="sequenceID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{8080029F-AAA4-AB46-89B3-8EDB0EFF552A}" name="virus_subfamily" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{DE16335A-748B-1842-A629-8E167CFD9609}" name="virus_genus" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{901DEBE6-9008-A143-B9BB-15E5D6B0159E}" name="virus_name" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{38A98292-EA6F-B744-A3E2-B5AD776188BE}" name="virus_full_name" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{69B3BC6F-80C4-EE43-8902-63CB5BD40EBB}" name="virus_other_name" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{E8E77199-1217-9047-B227-05D85E938F7E}" name="host_species" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{CE174F24-79B9-F54F-B4AA-6B3A8D8C4BF8}" name="assign_clade" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{19A65043-EC75-784A-8FDC-14CC3AC2C857}" name="assign_subclade" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{7480B5F5-AA96-0B43-A49C-DBA023807A5A}" name="virus_clade_ns" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{7E78A414-857B-CE47-95FC-ABE457B797CD}" name="virus_subclade_ns" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{BDC01F9C-03F5-A441-87D4-8B0A00507F22}" name="virus_clade_vp" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{BEAC9062-5AC4-2D4B-BF8A-EF4C231B9153}" name="virus_subclade_vp" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{30603152-4608-C847-ADA6-12243275347C}" name="lab_construct" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{FBC8F50D-4E86-7E4B-8A10-11D232E78A19}" name="accession-other" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -647,6 +830,14 @@
     <col min="5" max="5" width="33.33203125" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" customWidth="1"/>
     <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="17.5" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -706,40 +897,40 @@
       <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="6"/>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -751,40 +942,40 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="6"/>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -796,40 +987,40 @@
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="6"/>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -841,40 +1032,40 @@
       <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O5" s="6"/>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -886,40 +1077,40 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="6"/>
+      <c r="H6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -931,40 +1122,40 @@
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7" s="6"/>
+      <c r="H7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -976,40 +1167,40 @@
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" s="6"/>
+      <c r="H8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1021,40 +1212,40 @@
       <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="6"/>
+      <c r="H9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -1066,40 +1257,40 @@
       <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O10" s="6"/>
+      <c r="H10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1111,40 +1302,40 @@
       <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="6"/>
+      <c r="H11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -1156,40 +1347,40 @@
       <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O12" s="6"/>
+      <c r="H12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -1201,40 +1392,40 @@
       <c r="C13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="6"/>
+      <c r="H13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -1246,40 +1437,40 @@
       <c r="C14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="6"/>
+      <c r="H14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1291,42 +1482,46 @@
       <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>